--- a/data/cox_xlsx/FFARMS.CO.xlsx
+++ b/data/cox_xlsx/FFARMS.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="388">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -738,7 +738,7 @@
     <t>Deferred tax</t>
   </si>
   <si>
-    <t>Credit institutions</t>
+    <t>Credit institutions LT</t>
   </si>
   <si>
     <t>Capitalized Lease Obligations - Long-Term</t>
@@ -754,6 +754,9 @@
   </si>
   <si>
     <t>Other debts</t>
+  </si>
+  <si>
+    <t>Convertible bonds LT</t>
   </si>
   <si>
     <t>Total non-current liabilities</t>
@@ -1305,7 +1308,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1383,6 +1386,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -10710,9 +10716,7 @@
         <v>223</v>
       </c>
       <c r="B75" s="17"/>
-      <c r="C75" s="17">
-        <v>0.0</v>
-      </c>
+      <c r="C75" s="17"/>
       <c r="D75" s="17"/>
       <c r="E75" s="17"/>
       <c r="F75" s="17"/>
@@ -10859,41 +10863,41 @@
       <c r="A78" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B78" s="15">
-        <v>134.36</v>
-      </c>
-      <c r="C78" s="15">
-        <v>105.5</v>
-      </c>
-      <c r="D78" s="15">
-        <v>211.32</v>
-      </c>
-      <c r="E78" s="15">
-        <v>102.59</v>
-      </c>
-      <c r="F78" s="15">
-        <v>149.04</v>
-      </c>
-      <c r="G78" s="15">
-        <v>159.51</v>
+      <c r="B78" s="16">
+        <v>110.82000000000002</v>
+      </c>
+      <c r="C78" s="16">
+        <v>84.49</v>
+      </c>
+      <c r="D78" s="16">
+        <v>190.56</v>
+      </c>
+      <c r="E78" s="16">
+        <v>83.94</v>
+      </c>
+      <c r="F78" s="16">
+        <v>132.69</v>
+      </c>
+      <c r="G78" s="16">
+        <v>136.04999999999998</v>
       </c>
       <c r="H78" s="16">
-        <v>90.7</v>
+        <v>79.5</v>
       </c>
       <c r="I78" s="16">
         <v>57.53</v>
       </c>
-      <c r="J78" s="15">
+      <c r="J78" s="16">
         <v>113.96</v>
       </c>
-      <c r="K78" s="15">
+      <c r="K78" s="16">
         <v>102.8</v>
       </c>
       <c r="L78" s="16">
-        <v>43.11</v>
+        <v>36.43</v>
       </c>
       <c r="M78" s="16">
-        <v>35.22</v>
+        <v>30.689999999999998</v>
       </c>
       <c r="N78" s="16">
         <v>41.53</v>
@@ -11514,7 +11518,7 @@
       </c>
     </row>
     <row r="92" ht="15.0" customHeight="1">
-      <c r="A92" s="14" t="s">
+      <c r="A92" s="26" t="s">
         <v>239</v>
       </c>
       <c r="B92" s="15">
@@ -11780,8 +11784,8 @@
       <c r="T98" s="17"/>
     </row>
     <row r="99" ht="15.0" customHeight="1">
-      <c r="A99" s="14" t="s">
-        <v>232</v>
+      <c r="A99" s="26" t="s">
+        <v>245</v>
       </c>
       <c r="B99" s="15">
         <v>140.33</v>
@@ -11829,7 +11833,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B100" s="19">
         <v>1134.35</v>
@@ -11891,7 +11895,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B101" s="19">
         <v>1366.22</v>
@@ -11953,7 +11957,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B102" s="15">
         <v>175.9</v>
@@ -12015,7 +12019,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B103" s="21">
         <v>-77.11</v>
@@ -12077,7 +12081,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B104" s="15">
         <v>1193.82</v>
@@ -12139,7 +12143,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B105" s="17">
         <v>0.0</v>
@@ -12189,7 +12193,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B106" s="17"/>
       <c r="C106" s="17"/>
@@ -12229,7 +12233,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B107" s="17">
         <v>0.0</v>
@@ -12263,7 +12267,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B108" s="19">
         <v>1292.6</v>
@@ -12325,7 +12329,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B109" s="16">
         <v>0.09</v>
@@ -12351,7 +12355,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B110" s="20">
         <v>0.09</v>
@@ -12377,7 +12381,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B111" s="19">
         <v>1292.7</v>
@@ -12439,7 +12443,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B112" s="19">
         <v>2658.92</v>
@@ -12501,7 +12505,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B113" s="16">
         <v>11.15</v>
@@ -12563,7 +12567,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B114" s="16">
         <v>11.15</v>
@@ -12625,7 +12629,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B115" s="17">
         <v>0.0</v>
@@ -12687,7 +12691,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B116" s="17"/>
       <c r="C116" s="17"/>
@@ -12731,7 +12735,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B117" s="17"/>
       <c r="C117" s="17"/>
@@ -12769,7 +12773,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B118" s="17"/>
       <c r="C118" s="17"/>
@@ -12805,7 +12809,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B119" s="16">
         <v>74.14</v>
@@ -12857,7 +12861,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B120" s="15">
         <v>235.67</v>
@@ -12891,7 +12895,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B121" s="15">
         <v>483.71</v>
@@ -12927,7 +12931,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B122" s="17"/>
       <c r="C122" s="17"/>
@@ -12957,7 +12961,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B123" s="17"/>
       <c r="C123" s="17"/>
@@ -13005,7 +13009,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B124" s="17"/>
       <c r="C124" s="17"/>
@@ -13049,7 +13053,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B125" s="16">
         <v>23.54</v>
@@ -13101,7 +13105,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B126" s="16">
         <v>81.63</v>
@@ -13153,7 +13157,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B127" s="16">
         <v>11.11</v>
@@ -13191,7 +13195,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B128" s="16">
         <v>11.15</v>
@@ -13253,7 +13257,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B129" s="16">
         <v>1.0</v>
@@ -13315,7 +13319,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B130" s="17">
         <v>0.0</v>
@@ -13377,7 +13381,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B131" s="16">
         <v>11.15</v>
@@ -13439,7 +13443,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B132" s="15">
         <v>415.0</v>
@@ -13483,7 +13487,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B133" s="17"/>
       <c r="C133" s="17"/>
@@ -13519,7 +13523,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B134" s="17"/>
       <c r="C134" s="17"/>
@@ -13555,7 +13559,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B135" s="17"/>
       <c r="C135" s="17"/>
@@ -13587,7 +13591,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B136" s="17"/>
       <c r="C136" s="17"/>
@@ -14507,7 +14511,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -14854,61 +14858,61 @@
         <v>41</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -14975,7 +14979,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -15123,7 +15127,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -15175,7 +15179,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B22" s="16">
         <v>97.18</v>
@@ -15211,7 +15215,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -15237,7 +15241,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B24" s="21">
         <v>-6.22</v>
@@ -15479,7 +15483,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B28" s="16">
         <v>1.75</v>
@@ -15539,7 +15543,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B29" s="21">
         <v>-54.3</v>
@@ -15629,7 +15633,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B31" s="16">
         <v>1.34</v>
@@ -15671,7 +15675,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -15697,7 +15701,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B33" s="16">
         <v>35.83</v>
@@ -15723,7 +15727,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B34" s="16">
         <v>9.01</v>
@@ -15785,7 +15789,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B35" s="21">
         <v>-61.86</v>
@@ -15845,7 +15849,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B36" s="21">
         <v>-12.01</v>
@@ -15879,7 +15883,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B37" s="15">
         <v>192.49</v>
@@ -15919,7 +15923,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B38" s="15">
         <v>138.19</v>
@@ -15965,7 +15969,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
@@ -15991,7 +15995,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -16029,7 +16033,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
@@ -16061,7 +16065,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B42" s="17"/>
       <c r="C42" s="23">
@@ -16113,7 +16117,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="18" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B43" s="20">
         <v>73.32</v>
@@ -16175,7 +16179,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B44" s="17"/>
       <c r="C44" s="17">
@@ -16215,7 +16219,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B45" s="17">
         <v>0.0</v>
@@ -16245,7 +16249,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B46" s="17">
         <v>0.0</v>
@@ -16277,7 +16281,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
@@ -16307,7 +16311,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B48" s="16">
         <v>8.17</v>
@@ -16369,7 +16373,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -16397,7 +16401,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B50" s="25">
         <v>-147.4</v>
@@ -16459,7 +16463,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -16489,7 +16493,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -16533,7 +16537,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -16563,7 +16567,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -16595,15 +16599,15 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="B55" s="26">
+        <v>314</v>
+      </c>
+      <c r="B55" s="27">
         <v>-139.23</v>
       </c>
-      <c r="C55" s="26">
+      <c r="C55" s="27">
         <v>-298.68</v>
       </c>
-      <c r="D55" s="26">
+      <c r="D55" s="27">
         <v>-333.02</v>
       </c>
       <c r="E55" s="19">
@@ -16612,7 +16616,7 @@
       <c r="F55" s="22">
         <v>-19.02</v>
       </c>
-      <c r="G55" s="26">
+      <c r="G55" s="27">
         <v>-113.1</v>
       </c>
       <c r="H55" s="22">
@@ -16645,10 +16649,10 @@
       <c r="Q55" s="20">
         <v>10.76</v>
       </c>
-      <c r="R55" s="26">
+      <c r="R55" s="27">
         <v>-196.9</v>
       </c>
-      <c r="S55" s="26">
+      <c r="S55" s="27">
         <v>-139.25</v>
       </c>
       <c r="T55" s="22">
@@ -16657,7 +16661,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B56" s="17">
         <v>0.0</v>
@@ -16691,7 +16695,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -16723,7 +16727,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B58" s="17"/>
       <c r="C58" s="17">
@@ -16757,7 +16761,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B59" s="17"/>
       <c r="C59" s="17">
@@ -16805,7 +16809,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B60" s="16">
         <v>50.22</v>
@@ -16867,7 +16871,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B61" s="15">
         <v>138.5</v>
@@ -16907,7 +16911,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B62" s="21">
         <v>-53.37</v>
@@ -16947,7 +16951,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B63" s="21">
         <v>-14.4</v>
@@ -16983,7 +16987,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -17019,7 +17023,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B65" s="15">
         <v>151.03</v>
@@ -17045,7 +17049,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B66" s="21">
         <v>-27.07</v>
@@ -17071,7 +17075,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
@@ -17097,7 +17101,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B68" s="21">
         <v>-13.42</v>
@@ -17123,7 +17127,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B69" s="16">
         <v>8.66</v>
@@ -17149,7 +17153,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B70" s="17">
         <v>0.0</v>
@@ -17175,7 +17179,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="18" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B71" s="19">
         <v>240.15</v>
@@ -17186,7 +17190,7 @@
       <c r="D71" s="19">
         <v>162.8</v>
       </c>
-      <c r="E71" s="26">
+      <c r="E71" s="27">
         <v>-117.85</v>
       </c>
       <c r="F71" s="22">
@@ -17237,7 +17241,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -17265,7 +17269,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B73" s="17">
         <v>0.0</v>
@@ -17327,7 +17331,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B74" s="16">
         <v>40.84</v>
@@ -17389,7 +17393,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B75" s="15">
         <v>217.31</v>
@@ -17451,7 +17455,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B76" s="15">
         <v>174.24</v>
@@ -17501,7 +17505,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="18" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B77" s="19">
         <v>174.24</v>
@@ -17551,10 +17555,10 @@
       <c r="Q77" s="20">
         <v>8.68</v>
       </c>
-      <c r="R77" s="26">
+      <c r="R77" s="27">
         <v>-200.39</v>
       </c>
-      <c r="S77" s="26">
+      <c r="S77" s="27">
         <v>-157.34</v>
       </c>
       <c r="T77" s="19">
@@ -17563,7 +17567,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -17615,7 +17619,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B79" s="16">
         <v>82.59</v>
@@ -18586,7 +18590,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19054,7 +19058,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -19139,2134 +19143,2134 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="27" t="s">
-        <v>338</v>
-      </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
+      <c r="A20" s="28" t="s">
+        <v>339</v>
+      </c>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="29" t="s">
-        <v>338</v>
-      </c>
-      <c r="B21" s="30">
+      <c r="A21" s="30" t="s">
+        <v>339</v>
+      </c>
+      <c r="B21" s="31">
         <v>2118.49</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <v>1882.52</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>1704.26</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <v>1233.01</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <v>1356.7</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="31">
         <v>1203.19</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="31">
         <v>827.62</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="31">
         <v>691.89</v>
       </c>
-      <c r="J21" s="30">
+      <c r="J21" s="31">
         <v>493.99</v>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="31">
         <v>454.1</v>
       </c>
-      <c r="L21" s="30">
+      <c r="L21" s="31">
         <v>398.49</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="31">
         <v>361.34</v>
       </c>
-      <c r="N21" s="30">
+      <c r="N21" s="31">
         <v>224.48</v>
       </c>
-      <c r="O21" s="30">
+      <c r="O21" s="31">
         <v>296.15</v>
       </c>
-      <c r="P21" s="30">
+      <c r="P21" s="31">
         <v>362.93</v>
       </c>
-      <c r="Q21" s="30">
+      <c r="Q21" s="31">
         <v>342.27</v>
       </c>
-      <c r="R21" s="30">
+      <c r="R21" s="31">
         <v>411.48</v>
       </c>
-      <c r="S21" s="30">
+      <c r="S21" s="31">
         <v>506.35</v>
       </c>
-      <c r="T21" s="31"/>
+      <c r="T21" s="32"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="29" t="s">
-        <v>339</v>
-      </c>
-      <c r="B22" s="30">
+      <c r="A22" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="B22" s="31">
         <v>1794.22</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <v>1577.23</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="31">
         <v>1304.37</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <v>1060.82</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="31">
         <v>965.16</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="31">
         <v>742.36</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="31">
         <v>592.31</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="31">
         <v>511.01</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="31">
         <v>400.2</v>
       </c>
-      <c r="K22" s="30">
+      <c r="K22" s="31">
         <v>390.31</v>
       </c>
-      <c r="L22" s="30">
+      <c r="L22" s="31">
         <v>366.96</v>
       </c>
-      <c r="M22" s="30">
+      <c r="M22" s="31">
         <v>333.17</v>
       </c>
-      <c r="N22" s="30">
+      <c r="N22" s="31">
         <v>291.82</v>
       </c>
-      <c r="O22" s="30">
+      <c r="O22" s="31">
         <v>360.1</v>
       </c>
-      <c r="P22" s="31"/>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="27" t="s">
-        <v>340</v>
-      </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
+      <c r="A23" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>340</v>
-      </c>
-      <c r="B24" s="30">
+      <c r="A24" s="30" t="s">
+        <v>341</v>
+      </c>
+      <c r="B24" s="31">
         <v>1248.88</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <v>1008.93</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <v>1029.94</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <v>757.86</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="31">
         <v>690.35</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <v>553.63</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="31">
         <v>379.21</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="31">
         <v>370.39</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="31">
         <v>275.99</v>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="31">
         <v>249.14</v>
       </c>
-      <c r="L24" s="30">
+      <c r="L24" s="31">
         <v>255.15</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="31">
         <v>252.87</v>
       </c>
-      <c r="N24" s="30">
+      <c r="N24" s="31">
         <v>152.15</v>
       </c>
-      <c r="O24" s="30">
+      <c r="O24" s="31">
         <v>226.56</v>
       </c>
-      <c r="P24" s="30">
+      <c r="P24" s="31">
         <v>295.51</v>
       </c>
-      <c r="Q24" s="30">
+      <c r="Q24" s="31">
         <v>283.68</v>
       </c>
-      <c r="R24" s="30">
+      <c r="R24" s="31">
         <v>368.88</v>
       </c>
-      <c r="S24" s="30">
+      <c r="S24" s="31">
         <v>686.87</v>
       </c>
-      <c r="T24" s="30">
+      <c r="T24" s="31">
         <v>535.65</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="29" t="s">
-        <v>341</v>
-      </c>
-      <c r="B25" s="30">
+      <c r="A25" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="B25" s="31">
         <v>1024.89</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <v>863.13</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <v>702.14</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="31">
         <v>549.13</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="31">
         <v>479.27</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="31">
         <v>370.36</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="31">
         <v>317.21</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="31">
         <v>300.48</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="31">
         <v>247.06</v>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="31">
         <v>257.87</v>
       </c>
-      <c r="L25" s="30">
+      <c r="L25" s="31">
         <v>264.99</v>
       </c>
-      <c r="M25" s="30">
+      <c r="M25" s="31">
         <v>253.92</v>
       </c>
-      <c r="N25" s="30">
+      <c r="N25" s="31">
         <v>234.72</v>
       </c>
-      <c r="O25" s="30">
+      <c r="O25" s="31">
         <v>350.34</v>
       </c>
-      <c r="P25" s="30">
+      <c r="P25" s="31">
         <v>407.8</v>
       </c>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="31"/>
-      <c r="T25" s="31"/>
+      <c r="Q25" s="32"/>
+      <c r="R25" s="32"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="32"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="27" t="s">
-        <v>342</v>
-      </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
+      <c r="A26" s="28" t="s">
+        <v>343</v>
+      </c>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="29" t="s">
-        <v>343</v>
-      </c>
-      <c r="B27" s="30">
+      <c r="A27" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B27" s="31">
         <v>112.04</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>101.44</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>108.87</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="33">
         <v>96.41</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="33">
         <v>91.24</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="33">
         <v>87.63</v>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="33">
         <v>61.57</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="33">
         <v>72.09</v>
       </c>
-      <c r="J27" s="32">
+      <c r="J27" s="33">
         <v>58.57</v>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="33">
         <v>52.87</v>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="33">
         <v>54.15</v>
       </c>
-      <c r="M27" s="32">
+      <c r="M27" s="33">
         <v>53.66</v>
       </c>
-      <c r="N27" s="32">
+      <c r="N27" s="33">
         <v>32.29</v>
       </c>
-      <c r="O27" s="32">
+      <c r="O27" s="33">
         <v>48.08</v>
       </c>
-      <c r="P27" s="32">
+      <c r="P27" s="33">
         <v>62.71</v>
       </c>
-      <c r="Q27" s="32">
+      <c r="Q27" s="33">
         <v>60.2</v>
       </c>
-      <c r="R27" s="32">
+      <c r="R27" s="33">
         <v>78.28</v>
       </c>
-      <c r="S27" s="30">
+      <c r="S27" s="31">
         <v>145.76</v>
       </c>
-      <c r="T27" s="30">
+      <c r="T27" s="31">
         <v>113.67</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="29" t="s">
-        <v>344</v>
-      </c>
-      <c r="B28" s="30">
+      <c r="A28" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="B28" s="31">
         <v>111.16</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="31">
         <v>104.35</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="33">
         <v>92.09</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="33">
         <v>81.81</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="33">
         <v>78.87</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="33">
         <v>67.57</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="33">
         <v>62.23</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="33">
         <v>62.46</v>
       </c>
-      <c r="J28" s="32">
+      <c r="J28" s="33">
         <v>52.43</v>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="33">
         <v>54.72</v>
       </c>
-      <c r="L28" s="32">
+      <c r="L28" s="33">
         <v>56.23</v>
       </c>
-      <c r="M28" s="32">
+      <c r="M28" s="33">
         <v>53.89</v>
       </c>
-      <c r="N28" s="32">
+      <c r="N28" s="33">
         <v>49.81</v>
       </c>
-      <c r="O28" s="32">
+      <c r="O28" s="33">
         <v>74.35</v>
       </c>
-      <c r="P28" s="32">
+      <c r="P28" s="33">
         <v>86.54</v>
       </c>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
+      <c r="A29" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>346</v>
-      </c>
-      <c r="B30" s="33">
+      <c r="A30" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="B30" s="34">
         <v>-5.35</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="34">
         <v>-11.43</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="34">
         <v>-16.62</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="34">
         <v>-1.12</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="34">
         <v>-5.27</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="35">
         <v>3.15</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="34">
         <v>-5.35</v>
       </c>
-      <c r="I30" s="33">
+      <c r="I30" s="34">
         <v>-8.83</v>
       </c>
-      <c r="J30" s="33">
+      <c r="J30" s="34">
         <v>-8.03</v>
       </c>
-      <c r="K30" s="33">
+      <c r="K30" s="34">
         <v>-20.83</v>
       </c>
-      <c r="L30" s="33">
+      <c r="L30" s="34">
         <v>-18.62</v>
       </c>
-      <c r="M30" s="33">
+      <c r="M30" s="34">
         <v>-8.8</v>
       </c>
-      <c r="N30" s="33">
+      <c r="N30" s="34">
         <v>-11.6</v>
       </c>
-      <c r="O30" s="33">
+      <c r="O30" s="34">
         <v>-1.98</v>
       </c>
-      <c r="P30" s="33">
+      <c r="P30" s="34">
         <v>-6.27</v>
       </c>
-      <c r="Q30" s="33">
+      <c r="Q30" s="34">
         <v>-30.09</v>
       </c>
-      <c r="R30" s="33">
+      <c r="R30" s="34">
         <v>-58.06</v>
       </c>
-      <c r="S30" s="33">
+      <c r="S30" s="34">
         <v>-13.89</v>
       </c>
-      <c r="T30" s="34"/>
+      <c r="T30" s="35"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="29" t="s">
-        <v>347</v>
-      </c>
-      <c r="B31" s="33">
+      <c r="A31" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="B31" s="34">
         <v>-8.11</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="34">
         <v>-6.52</v>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="34">
         <v>-5.34</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="34">
         <v>-3.1</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="34">
         <v>-4.45</v>
       </c>
-      <c r="G31" s="33">
+      <c r="G31" s="34">
         <v>-6.87</v>
       </c>
-      <c r="H31" s="33">
+      <c r="H31" s="34">
         <v>-11.94</v>
       </c>
-      <c r="I31" s="33">
+      <c r="I31" s="34">
         <v>-12.6</v>
       </c>
-      <c r="J31" s="33">
+      <c r="J31" s="34">
         <v>-13.41</v>
       </c>
-      <c r="K31" s="33">
+      <c r="K31" s="34">
         <v>-12.13</v>
       </c>
-      <c r="L31" s="33">
+      <c r="L31" s="34">
         <v>-9.07</v>
       </c>
-      <c r="M31" s="33">
+      <c r="M31" s="34">
         <v>-12.01</v>
       </c>
-      <c r="N31" s="33">
+      <c r="N31" s="34">
         <v>-23.54</v>
       </c>
-      <c r="O31" s="33">
+      <c r="O31" s="34">
         <v>-20.94</v>
       </c>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="34"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="27" t="s">
-        <v>348</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
+      <c r="A32" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="29" t="s">
-        <v>349</v>
-      </c>
-      <c r="B33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="C33" s="34">
+      <c r="A33" s="30" t="s">
+        <v>350</v>
+      </c>
+      <c r="B33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="C33" s="35">
         <v>1.41</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="35">
         <v>1.1</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="35">
         <v>1.05</v>
       </c>
-      <c r="F33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="G33" s="34">
+      <c r="F33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="G33" s="35">
         <v>0.8</v>
       </c>
-      <c r="H33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="I33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="J33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="K33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="M33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="N33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="O33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="P33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="Q33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="R33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="S33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="T33" s="34"/>
+      <c r="H33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="I33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="J33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="K33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="L33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="M33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="O33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="P33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="Q33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="R33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="S33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="T33" s="35"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="29" t="s">
-        <v>350</v>
-      </c>
-      <c r="B34" s="34">
+      <c r="A34" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="B34" s="35">
         <v>0.72</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="35">
         <v>0.89</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="35">
         <v>0.65</v>
       </c>
-      <c r="E34" s="34">
+      <c r="E34" s="35">
         <v>0.42</v>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="35">
         <v>0.19</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="35">
         <v>0.21</v>
       </c>
-      <c r="H34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="I34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="J34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="M34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="N34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="O34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="34"/>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
+      <c r="H34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="I34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="J34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="K34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="M34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="35"/>
+      <c r="R34" s="35"/>
+      <c r="S34" s="35"/>
+      <c r="T34" s="35"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="29" t="s">
-        <v>351</v>
-      </c>
-      <c r="B35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="C35" s="34">
+      <c r="A35" s="30" t="s">
+        <v>352</v>
+      </c>
+      <c r="B35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="C35" s="35">
         <v>1.41</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="35">
         <v>1.1</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="35">
         <v>1.05</v>
       </c>
-      <c r="F35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="G35" s="34">
+      <c r="F35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="35">
         <v>0.8</v>
       </c>
-      <c r="H35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="J35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="M35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="N35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="O35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="P35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="Q35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="R35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="S35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="T35" s="34"/>
+      <c r="H35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="J35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="M35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="P35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="Q35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="R35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="S35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="T35" s="35"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="29" t="s">
-        <v>352</v>
-      </c>
-      <c r="B36" s="34">
+      <c r="A36" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="B36" s="35">
         <v>0.72</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="35">
         <v>0.89</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="35">
         <v>0.65</v>
       </c>
-      <c r="E36" s="34">
+      <c r="E36" s="35">
         <v>0.42</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="35">
         <v>0.19</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="35">
         <v>0.21</v>
       </c>
-      <c r="H36" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="I36" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="J36" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="K36" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="L36" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="M36" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="N36" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="O36" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-      <c r="R36" s="34"/>
-      <c r="S36" s="34"/>
-      <c r="T36" s="34"/>
+      <c r="H36" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="I36" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="J36" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="K36" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="L36" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="M36" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="O36" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="35"/>
+      <c r="R36" s="35"/>
+      <c r="S36" s="35"/>
+      <c r="T36" s="35"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="27" t="s">
-        <v>353</v>
-      </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
+      <c r="A37" s="28" t="s">
+        <v>354</v>
+      </c>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="29"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="29" t="s">
-        <v>354</v>
-      </c>
-      <c r="B38" s="32">
+      <c r="A38" s="30" t="s">
+        <v>355</v>
+      </c>
+      <c r="B38" s="33">
         <v>0.97</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="33">
         <v>0.93</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="33">
         <v>1.07</v>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="33">
         <v>1.06</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="33">
         <v>1.01</v>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="33">
         <v>1.07</v>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="33">
         <v>0.77</v>
       </c>
-      <c r="I38" s="32">
+      <c r="I38" s="33">
         <v>0.89</v>
       </c>
-      <c r="J38" s="32">
+      <c r="J38" s="33">
         <v>0.77</v>
       </c>
-      <c r="K38" s="32">
+      <c r="K38" s="33">
         <v>0.63</v>
       </c>
-      <c r="L38" s="32">
+      <c r="L38" s="33">
         <v>0.64</v>
       </c>
-      <c r="M38" s="32">
+      <c r="M38" s="33">
         <v>0.71</v>
       </c>
-      <c r="N38" s="32">
+      <c r="N38" s="33">
         <v>0.49</v>
       </c>
-      <c r="O38" s="32">
+      <c r="O38" s="33">
         <v>0.63</v>
       </c>
-      <c r="P38" s="32">
+      <c r="P38" s="33">
         <v>0.83</v>
       </c>
-      <c r="Q38" s="32">
+      <c r="Q38" s="33">
         <v>0.72</v>
       </c>
-      <c r="R38" s="32">
+      <c r="R38" s="33">
         <v>0.72</v>
       </c>
-      <c r="S38" s="32">
+      <c r="S38" s="33">
         <v>1.53</v>
       </c>
-      <c r="T38" s="31"/>
+      <c r="T38" s="32"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="29" t="s">
-        <v>355</v>
-      </c>
-      <c r="B39" s="32">
+      <c r="A39" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="B39" s="33">
         <v>1.01</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="33">
         <v>1.03</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="33">
         <v>1.0</v>
       </c>
-      <c r="E39" s="32">
+      <c r="E39" s="33">
         <v>0.96</v>
       </c>
-      <c r="F39" s="32">
+      <c r="F39" s="33">
         <v>0.9</v>
       </c>
-      <c r="G39" s="32">
+      <c r="G39" s="33">
         <v>0.83</v>
       </c>
-      <c r="H39" s="32">
+      <c r="H39" s="33">
         <v>0.74</v>
       </c>
-      <c r="I39" s="32">
+      <c r="I39" s="33">
         <v>0.72</v>
       </c>
-      <c r="J39" s="32">
+      <c r="J39" s="33">
         <v>0.64</v>
       </c>
-      <c r="K39" s="32">
+      <c r="K39" s="33">
         <v>0.62</v>
       </c>
-      <c r="L39" s="32">
+      <c r="L39" s="33">
         <v>0.66</v>
       </c>
-      <c r="M39" s="32">
+      <c r="M39" s="33">
         <v>0.68</v>
       </c>
-      <c r="N39" s="32">
+      <c r="N39" s="33">
         <v>0.68</v>
       </c>
-      <c r="O39" s="32">
+      <c r="O39" s="33">
         <v>0.91</v>
       </c>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="31"/>
-      <c r="R39" s="31"/>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="27" t="s">
-        <v>356</v>
-      </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
+      <c r="A40" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="29"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="29" t="s">
-        <v>357</v>
-      </c>
-      <c r="B41" s="32">
+      <c r="A41" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="B41" s="33">
         <v>0.99</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="33">
         <v>0.95</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="33">
         <v>1.09</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="33">
         <v>1.09</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="33">
         <v>1.05</v>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="33">
         <v>1.12</v>
       </c>
-      <c r="H41" s="32">
+      <c r="H41" s="33">
         <v>0.81</v>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="33">
         <v>0.94</v>
       </c>
-      <c r="J41" s="32">
+      <c r="J41" s="33">
         <v>0.83</v>
       </c>
-      <c r="K41" s="32">
+      <c r="K41" s="33">
         <v>0.68</v>
       </c>
-      <c r="L41" s="32">
+      <c r="L41" s="33">
         <v>0.69</v>
       </c>
-      <c r="M41" s="32">
+      <c r="M41" s="33">
         <v>0.75</v>
       </c>
-      <c r="N41" s="32">
+      <c r="N41" s="33">
         <v>0.52</v>
       </c>
-      <c r="O41" s="32">
+      <c r="O41" s="33">
         <v>0.67</v>
       </c>
-      <c r="P41" s="32">
+      <c r="P41" s="33">
         <v>0.89</v>
       </c>
-      <c r="Q41" s="32">
+      <c r="Q41" s="33">
         <v>0.78</v>
       </c>
-      <c r="R41" s="32">
+      <c r="R41" s="33">
         <v>0.77</v>
       </c>
-      <c r="S41" s="32">
+      <c r="S41" s="33">
         <v>1.64</v>
       </c>
-      <c r="T41" s="31"/>
+      <c r="T41" s="32"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="29" t="s">
-        <v>358</v>
-      </c>
-      <c r="B42" s="32">
+      <c r="A42" s="30" t="s">
+        <v>359</v>
+      </c>
+      <c r="B42" s="33">
         <v>1.03</v>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="33">
         <v>1.06</v>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="33">
         <v>1.04</v>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="33">
         <v>1.01</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="33">
         <v>0.95</v>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="33">
         <v>0.87</v>
       </c>
-      <c r="H42" s="32">
+      <c r="H42" s="33">
         <v>0.79</v>
       </c>
-      <c r="I42" s="32">
+      <c r="I42" s="33">
         <v>0.77</v>
       </c>
-      <c r="J42" s="32">
+      <c r="J42" s="33">
         <v>0.69</v>
       </c>
-      <c r="K42" s="32">
+      <c r="K42" s="33">
         <v>0.66</v>
       </c>
-      <c r="L42" s="32">
+      <c r="L42" s="33">
         <v>0.71</v>
       </c>
-      <c r="M42" s="32">
+      <c r="M42" s="33">
         <v>0.72</v>
       </c>
-      <c r="N42" s="32">
+      <c r="N42" s="33">
         <v>0.73</v>
       </c>
-      <c r="O42" s="32">
+      <c r="O42" s="33">
         <v>0.97</v>
       </c>
-      <c r="P42" s="31"/>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
+      <c r="P42" s="32"/>
+      <c r="Q42" s="32"/>
+      <c r="R42" s="32"/>
+      <c r="S42" s="32"/>
+      <c r="T42" s="32"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="27" t="s">
-        <v>359</v>
-      </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="28"/>
-      <c r="S43" s="28"/>
-      <c r="T43" s="28"/>
+      <c r="A43" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="29"/>
+      <c r="T43" s="29"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="29" t="s">
-        <v>360</v>
-      </c>
-      <c r="B44" s="32">
+      <c r="A44" s="30" t="s">
+        <v>361</v>
+      </c>
+      <c r="B44" s="33">
         <v>1.69</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <v>1.27</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="33">
         <v>1.6</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="33">
         <v>1.71</v>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="33">
         <v>1.78</v>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="33">
         <v>1.17</v>
       </c>
-      <c r="H44" s="32">
+      <c r="H44" s="33">
         <v>0.96</v>
       </c>
-      <c r="I44" s="32">
+      <c r="I44" s="33">
         <v>1.2</v>
       </c>
-      <c r="J44" s="32">
+      <c r="J44" s="33">
         <v>1.31</v>
       </c>
-      <c r="K44" s="32">
+      <c r="K44" s="33">
         <v>1.36</v>
       </c>
-      <c r="L44" s="32">
+      <c r="L44" s="33">
         <v>1.68</v>
       </c>
-      <c r="M44" s="32">
+      <c r="M44" s="33">
         <v>1.67</v>
       </c>
-      <c r="N44" s="32">
+      <c r="N44" s="33">
         <v>1.43</v>
       </c>
-      <c r="O44" s="32">
+      <c r="O44" s="33">
         <v>1.68</v>
       </c>
-      <c r="P44" s="32">
+      <c r="P44" s="33">
         <v>3.32</v>
       </c>
-      <c r="Q44" s="32">
+      <c r="Q44" s="33">
         <v>3.36</v>
       </c>
-      <c r="R44" s="32">
+      <c r="R44" s="33">
         <v>4.75</v>
       </c>
-      <c r="S44" s="32">
+      <c r="S44" s="33">
         <v>11.09</v>
       </c>
-      <c r="T44" s="31"/>
+      <c r="T44" s="32"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="29" t="s">
-        <v>361</v>
-      </c>
-      <c r="B45" s="32">
+      <c r="A45" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="B45" s="33">
         <v>1.59</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="33">
         <v>1.47</v>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="33">
         <v>1.41</v>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="33">
         <v>1.33</v>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="33">
         <v>1.25</v>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="33">
         <v>1.18</v>
       </c>
-      <c r="H45" s="32">
+      <c r="H45" s="33">
         <v>1.25</v>
       </c>
-      <c r="I45" s="32">
+      <c r="I45" s="33">
         <v>1.41</v>
       </c>
-      <c r="J45" s="32">
+      <c r="J45" s="33">
         <v>1.48</v>
       </c>
-      <c r="K45" s="32">
+      <c r="K45" s="33">
         <v>1.57</v>
       </c>
-      <c r="L45" s="32">
+      <c r="L45" s="33">
         <v>1.87</v>
       </c>
-      <c r="M45" s="32">
+      <c r="M45" s="33">
         <v>2.13</v>
       </c>
-      <c r="N45" s="32">
+      <c r="N45" s="33">
         <v>2.61</v>
       </c>
-      <c r="O45" s="32">
+      <c r="O45" s="33">
         <v>4.13</v>
       </c>
-      <c r="P45" s="31"/>
-      <c r="Q45" s="31"/>
-      <c r="R45" s="31"/>
-      <c r="S45" s="31"/>
-      <c r="T45" s="31"/>
+      <c r="P45" s="32"/>
+      <c r="Q45" s="32"/>
+      <c r="R45" s="32"/>
+      <c r="S45" s="32"/>
+      <c r="T45" s="32"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="27" t="s">
-        <v>362</v>
-      </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="28"/>
-      <c r="S46" s="28"/>
-      <c r="T46" s="28"/>
+      <c r="A46" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="29" t="s">
-        <v>363</v>
-      </c>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="32">
+      <c r="A47" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="33">
         <v>31.75</v>
       </c>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-      <c r="K47" s="31"/>
-      <c r="L47" s="31"/>
-      <c r="M47" s="31"/>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="31"/>
-      <c r="R47" s="31"/>
-      <c r="S47" s="31"/>
-      <c r="T47" s="31"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="32"/>
+      <c r="M47" s="32"/>
+      <c r="N47" s="32"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="32"/>
+      <c r="R47" s="32"/>
+      <c r="S47" s="32"/>
+      <c r="T47" s="32"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="27" t="s">
-        <v>364</v>
-      </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="28"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="28"/>
-      <c r="M48" s="28"/>
-      <c r="N48" s="28"/>
-      <c r="O48" s="28"/>
-      <c r="P48" s="28"/>
-      <c r="Q48" s="28"/>
-      <c r="R48" s="28"/>
-      <c r="S48" s="28"/>
-      <c r="T48" s="28"/>
+      <c r="A48" s="28" t="s">
+        <v>365</v>
+      </c>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="29"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="29"/>
+      <c r="S48" s="29"/>
+      <c r="T48" s="29"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="29" t="s">
-        <v>365</v>
-      </c>
-      <c r="B49" s="32">
+      <c r="A49" s="30" t="s">
+        <v>366</v>
+      </c>
+      <c r="B49" s="33">
         <v>11.3</v>
       </c>
-      <c r="C49" s="32">
+      <c r="C49" s="33">
         <v>8.61</v>
       </c>
-      <c r="D49" s="32">
+      <c r="D49" s="33">
         <v>6.77</v>
       </c>
-      <c r="E49" s="32">
+      <c r="E49" s="33">
         <v>9.19</v>
       </c>
-      <c r="F49" s="32">
+      <c r="F49" s="33">
         <v>9.19</v>
       </c>
-      <c r="G49" s="32">
+      <c r="G49" s="33">
         <v>6.44</v>
       </c>
-      <c r="H49" s="32">
+      <c r="H49" s="33">
         <v>7.19</v>
       </c>
-      <c r="I49" s="32">
+      <c r="I49" s="33">
         <v>9.33</v>
       </c>
-      <c r="J49" s="32">
+      <c r="J49" s="33">
         <v>20.97</v>
       </c>
-      <c r="K49" s="30">
+      <c r="K49" s="31">
         <v>108.74</v>
       </c>
-      <c r="L49" s="32">
+      <c r="L49" s="33">
         <v>8.5</v>
       </c>
-      <c r="M49" s="32">
+      <c r="M49" s="33">
         <v>11.36</v>
       </c>
-      <c r="N49" s="31"/>
-      <c r="O49" s="32">
+      <c r="N49" s="32"/>
+      <c r="O49" s="33">
         <v>7.97</v>
       </c>
-      <c r="P49" s="32">
+      <c r="P49" s="33">
         <v>32.42</v>
       </c>
-      <c r="Q49" s="31"/>
-      <c r="R49" s="31"/>
-      <c r="S49" s="32">
+      <c r="Q49" s="32"/>
+      <c r="R49" s="32"/>
+      <c r="S49" s="33">
         <v>46.8</v>
       </c>
-      <c r="T49" s="31"/>
+      <c r="T49" s="32"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="29" t="s">
-        <v>366</v>
-      </c>
-      <c r="B50" s="32">
+      <c r="A50" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="B50" s="33">
         <v>8.72</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="33">
         <v>7.82</v>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="33">
         <v>7.59</v>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="33">
         <v>8.11</v>
       </c>
-      <c r="F50" s="32">
+      <c r="F50" s="33">
         <v>8.76</v>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="33">
         <v>10.14</v>
       </c>
-      <c r="H50" s="32">
+      <c r="H50" s="33">
         <v>11.6</v>
       </c>
-      <c r="I50" s="32">
+      <c r="I50" s="33">
         <v>13.13</v>
       </c>
-      <c r="J50" s="32">
+      <c r="J50" s="33">
         <v>19.77</v>
       </c>
-      <c r="K50" s="32">
+      <c r="K50" s="33">
         <v>14.81</v>
       </c>
-      <c r="L50" s="32">
+      <c r="L50" s="33">
         <v>14.63</v>
       </c>
-      <c r="M50" s="32">
+      <c r="M50" s="33">
         <v>33.97</v>
       </c>
-      <c r="N50" s="30">
+      <c r="N50" s="31">
         <v>111.46</v>
       </c>
-      <c r="O50" s="32">
+      <c r="O50" s="33">
         <v>55.04</v>
       </c>
-      <c r="P50" s="31"/>
-      <c r="Q50" s="31"/>
-      <c r="R50" s="31"/>
-      <c r="S50" s="31"/>
-      <c r="T50" s="31"/>
+      <c r="P50" s="32"/>
+      <c r="Q50" s="32"/>
+      <c r="R50" s="32"/>
+      <c r="S50" s="32"/>
+      <c r="T50" s="32"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="27" t="s">
-        <v>367</v>
-      </c>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28"/>
-      <c r="N51" s="28"/>
-      <c r="O51" s="28"/>
-      <c r="P51" s="28"/>
-      <c r="Q51" s="28"/>
-      <c r="R51" s="28"/>
-      <c r="S51" s="28"/>
-      <c r="T51" s="28"/>
+      <c r="A51" s="28" t="s">
+        <v>368</v>
+      </c>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29"/>
+      <c r="M51" s="29"/>
+      <c r="N51" s="29"/>
+      <c r="O51" s="29"/>
+      <c r="P51" s="29"/>
+      <c r="Q51" s="29"/>
+      <c r="R51" s="29"/>
+      <c r="S51" s="29"/>
+      <c r="T51" s="29"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="B52" s="32">
+      <c r="A52" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="B52" s="33">
         <v>54.38</v>
       </c>
-      <c r="C52" s="32">
+      <c r="C52" s="33">
         <v>25.51</v>
       </c>
-      <c r="D52" s="32">
+      <c r="D52" s="33">
         <v>12.0</v>
       </c>
-      <c r="E52" s="32">
+      <c r="E52" s="33">
         <v>20.75</v>
       </c>
-      <c r="F52" s="32">
+      <c r="F52" s="33">
         <v>26.22</v>
       </c>
-      <c r="G52" s="32">
+      <c r="G52" s="33">
         <v>19.97</v>
       </c>
-      <c r="H52" s="32">
+      <c r="H52" s="33">
         <v>35.15</v>
       </c>
-      <c r="I52" s="32">
+      <c r="I52" s="33">
         <v>83.36</v>
       </c>
-      <c r="J52" s="31"/>
-      <c r="K52" s="31"/>
-      <c r="L52" s="32">
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="33">
         <v>29.71</v>
       </c>
-      <c r="M52" s="32">
+      <c r="M52" s="33">
         <v>81.04</v>
       </c>
-      <c r="N52" s="31"/>
-      <c r="O52" s="32">
+      <c r="N52" s="32"/>
+      <c r="O52" s="33">
         <v>24.18</v>
       </c>
-      <c r="P52" s="31"/>
-      <c r="Q52" s="31"/>
-      <c r="R52" s="31"/>
-      <c r="S52" s="30">
+      <c r="P52" s="32"/>
+      <c r="Q52" s="32"/>
+      <c r="R52" s="32"/>
+      <c r="S52" s="31">
         <v>238.57</v>
       </c>
-      <c r="T52" s="31"/>
+      <c r="T52" s="32"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="29" t="s">
-        <v>369</v>
-      </c>
-      <c r="B53" s="32">
+      <c r="A53" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="B53" s="33">
         <v>21.6</v>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="33">
         <v>18.97</v>
       </c>
-      <c r="D53" s="32">
+      <c r="D53" s="33">
         <v>19.2</v>
       </c>
-      <c r="E53" s="32">
+      <c r="E53" s="33">
         <v>27.06</v>
       </c>
-      <c r="F53" s="32">
+      <c r="F53" s="33">
         <v>55.74</v>
       </c>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="31"/>
-      <c r="N53" s="31"/>
-      <c r="O53" s="31"/>
-      <c r="P53" s="31"/>
-      <c r="Q53" s="31"/>
-      <c r="R53" s="31"/>
-      <c r="S53" s="31"/>
-      <c r="T53" s="31"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="32"/>
+      <c r="M53" s="32"/>
+      <c r="N53" s="32"/>
+      <c r="O53" s="32"/>
+      <c r="P53" s="32"/>
+      <c r="Q53" s="32"/>
+      <c r="R53" s="32"/>
+      <c r="S53" s="32"/>
+      <c r="T53" s="32"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="27" t="s">
-        <v>370</v>
-      </c>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="28"/>
-      <c r="I54" s="28"/>
-      <c r="J54" s="28"/>
-      <c r="K54" s="28"/>
-      <c r="L54" s="28"/>
-      <c r="M54" s="28"/>
-      <c r="N54" s="28"/>
-      <c r="O54" s="28"/>
-      <c r="P54" s="28"/>
-      <c r="Q54" s="28"/>
-      <c r="R54" s="28"/>
-      <c r="S54" s="28"/>
-      <c r="T54" s="28"/>
+      <c r="A54" s="28" t="s">
+        <v>371</v>
+      </c>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="29"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
+      <c r="L54" s="29"/>
+      <c r="M54" s="29"/>
+      <c r="N54" s="29"/>
+      <c r="O54" s="29"/>
+      <c r="P54" s="29"/>
+      <c r="Q54" s="29"/>
+      <c r="R54" s="29"/>
+      <c r="S54" s="29"/>
+      <c r="T54" s="29"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="29" t="s">
-        <v>371</v>
-      </c>
-      <c r="B55" s="32">
+      <c r="A55" s="30" t="s">
+        <v>372</v>
+      </c>
+      <c r="B55" s="33">
         <v>23.75</v>
       </c>
-      <c r="C55" s="32">
+      <c r="C55" s="33">
         <v>71.37</v>
       </c>
-      <c r="D55" s="32">
+      <c r="D55" s="33">
         <v>42.88</v>
       </c>
-      <c r="E55" s="32">
+      <c r="E55" s="33">
         <v>31.34</v>
       </c>
-      <c r="F55" s="32">
+      <c r="F55" s="33">
         <v>21.5</v>
       </c>
-      <c r="G55" s="32">
+      <c r="G55" s="33">
         <v>25.56</v>
       </c>
-      <c r="H55" s="31"/>
-      <c r="I55" s="31"/>
-      <c r="J55" s="31"/>
-      <c r="K55" s="31"/>
-      <c r="L55" s="31"/>
-      <c r="M55" s="31"/>
-      <c r="N55" s="31"/>
-      <c r="O55" s="31"/>
-      <c r="P55" s="31"/>
-      <c r="Q55" s="31"/>
-      <c r="R55" s="31"/>
-      <c r="S55" s="32">
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="32"/>
+      <c r="M55" s="32"/>
+      <c r="N55" s="32"/>
+      <c r="O55" s="32"/>
+      <c r="P55" s="32"/>
+      <c r="Q55" s="32"/>
+      <c r="R55" s="32"/>
+      <c r="S55" s="33">
         <v>20.63</v>
       </c>
-      <c r="T55" s="31"/>
+      <c r="T55" s="32"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="29" t="s">
-        <v>372</v>
-      </c>
-      <c r="B56" s="32">
+      <c r="A56" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="B56" s="33">
         <v>1.01</v>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="33">
         <v>1.03</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="33">
         <v>1.0</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="33">
         <v>0.96</v>
       </c>
-      <c r="F56" s="32">
+      <c r="F56" s="33">
         <v>0.9</v>
       </c>
-      <c r="G56" s="32">
+      <c r="G56" s="33">
         <v>0.83</v>
       </c>
-      <c r="H56" s="32">
+      <c r="H56" s="33">
         <v>0.74</v>
       </c>
-      <c r="I56" s="32">
+      <c r="I56" s="33">
         <v>0.72</v>
       </c>
-      <c r="J56" s="32">
+      <c r="J56" s="33">
         <v>0.64</v>
       </c>
-      <c r="K56" s="32">
+      <c r="K56" s="33">
         <v>0.62</v>
       </c>
-      <c r="L56" s="32">
+      <c r="L56" s="33">
         <v>0.66</v>
       </c>
-      <c r="M56" s="32">
+      <c r="M56" s="33">
         <v>0.68</v>
       </c>
-      <c r="N56" s="32">
+      <c r="N56" s="33">
         <v>0.68</v>
       </c>
-      <c r="O56" s="32">
+      <c r="O56" s="33">
         <v>0.91</v>
       </c>
-      <c r="P56" s="31"/>
-      <c r="Q56" s="31"/>
-      <c r="R56" s="31"/>
-      <c r="S56" s="31"/>
-      <c r="T56" s="31"/>
+      <c r="P56" s="32"/>
+      <c r="Q56" s="32"/>
+      <c r="R56" s="32"/>
+      <c r="S56" s="32"/>
+      <c r="T56" s="32"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="27" t="s">
-        <v>373</v>
-      </c>
-      <c r="B57" s="28"/>
-      <c r="C57" s="28"/>
-      <c r="D57" s="28"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="28"/>
-      <c r="J57" s="28"/>
-      <c r="K57" s="28"/>
-      <c r="L57" s="28"/>
-      <c r="M57" s="28"/>
-      <c r="N57" s="28"/>
-      <c r="O57" s="28"/>
-      <c r="P57" s="28"/>
-      <c r="Q57" s="28"/>
-      <c r="R57" s="28"/>
-      <c r="S57" s="28"/>
-      <c r="T57" s="28"/>
+      <c r="A57" s="28" t="s">
+        <v>374</v>
+      </c>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="29"/>
+      <c r="J57" s="29"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="29"/>
+      <c r="M57" s="29"/>
+      <c r="N57" s="29"/>
+      <c r="O57" s="29"/>
+      <c r="P57" s="29"/>
+      <c r="Q57" s="29"/>
+      <c r="R57" s="29"/>
+      <c r="S57" s="29"/>
+      <c r="T57" s="29"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="29" t="s">
-        <v>374</v>
-      </c>
-      <c r="B58" s="35">
+      <c r="A58" s="30" t="s">
+        <v>375</v>
+      </c>
+      <c r="B58" s="36">
         <v>-1.07</v>
       </c>
-      <c r="C58" s="35">
+      <c r="C58" s="36">
         <v>-0.43</v>
       </c>
-      <c r="D58" s="32">
+      <c r="D58" s="33">
         <v>0.14</v>
       </c>
-      <c r="E58" s="32">
+      <c r="E58" s="33">
         <v>0.52</v>
       </c>
-      <c r="F58" s="35">
+      <c r="F58" s="36">
         <v>-1.02</v>
       </c>
-      <c r="G58" s="32">
+      <c r="G58" s="33">
         <v>0.13</v>
       </c>
-      <c r="H58" s="32">
+      <c r="H58" s="33">
         <v>0.34</v>
       </c>
-      <c r="I58" s="32">
+      <c r="I58" s="33">
         <v>0.67</v>
       </c>
-      <c r="J58" s="31"/>
-      <c r="K58" s="31"/>
-      <c r="L58" s="32">
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="33">
         <v>0.19</v>
       </c>
-      <c r="M58" s="32">
+      <c r="M58" s="33">
         <v>0.74</v>
       </c>
-      <c r="N58" s="31"/>
-      <c r="O58" s="32">
+      <c r="N58" s="32"/>
+      <c r="O58" s="33">
         <v>0.12</v>
       </c>
-      <c r="P58" s="31"/>
-      <c r="Q58" s="31"/>
-      <c r="R58" s="31"/>
-      <c r="S58" s="31"/>
-      <c r="T58" s="31"/>
+      <c r="P58" s="32"/>
+      <c r="Q58" s="32"/>
+      <c r="R58" s="32"/>
+      <c r="S58" s="32"/>
+      <c r="T58" s="32"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="29" t="s">
-        <v>375</v>
-      </c>
-      <c r="B59" s="35">
+      <c r="A59" s="30" t="s">
+        <v>376</v>
+      </c>
+      <c r="B59" s="36">
         <v>-1.26</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="33">
         <v>1.27</v>
       </c>
-      <c r="D59" s="32">
+      <c r="D59" s="33">
         <v>0.33</v>
       </c>
-      <c r="E59" s="31"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="31"/>
-      <c r="I59" s="31"/>
-      <c r="J59" s="31"/>
-      <c r="K59" s="31"/>
-      <c r="L59" s="31"/>
-      <c r="M59" s="31"/>
-      <c r="N59" s="31"/>
-      <c r="O59" s="31"/>
-      <c r="P59" s="31"/>
-      <c r="Q59" s="31"/>
-      <c r="R59" s="31"/>
-      <c r="S59" s="31"/>
-      <c r="T59" s="31"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="32"/>
+      <c r="L59" s="32"/>
+      <c r="M59" s="32"/>
+      <c r="N59" s="32"/>
+      <c r="O59" s="32"/>
+      <c r="P59" s="32"/>
+      <c r="Q59" s="32"/>
+      <c r="R59" s="32"/>
+      <c r="S59" s="32"/>
+      <c r="T59" s="32"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="27" t="s">
-        <v>376</v>
-      </c>
-      <c r="B60" s="28"/>
-      <c r="C60" s="28"/>
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="28"/>
-      <c r="J60" s="28"/>
-      <c r="K60" s="28"/>
-      <c r="L60" s="28"/>
-      <c r="M60" s="28"/>
-      <c r="N60" s="28"/>
-      <c r="O60" s="28"/>
-      <c r="P60" s="28"/>
-      <c r="Q60" s="28"/>
-      <c r="R60" s="28"/>
-      <c r="S60" s="28"/>
-      <c r="T60" s="28"/>
+      <c r="A60" s="28" t="s">
+        <v>377</v>
+      </c>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
+      <c r="E60" s="29"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="29"/>
+      <c r="H60" s="29"/>
+      <c r="I60" s="29"/>
+      <c r="J60" s="29"/>
+      <c r="K60" s="29"/>
+      <c r="L60" s="29"/>
+      <c r="M60" s="29"/>
+      <c r="N60" s="29"/>
+      <c r="O60" s="29"/>
+      <c r="P60" s="29"/>
+      <c r="Q60" s="29"/>
+      <c r="R60" s="29"/>
+      <c r="S60" s="29"/>
+      <c r="T60" s="29"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="29" t="s">
-        <v>377</v>
-      </c>
-      <c r="B61" s="32">
+      <c r="A61" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="B61" s="33">
         <v>2.55</v>
       </c>
-      <c r="C61" s="32">
+      <c r="C61" s="33">
         <v>2.4</v>
       </c>
-      <c r="D61" s="32">
+      <c r="D61" s="33">
         <v>2.47</v>
       </c>
-      <c r="E61" s="32">
+      <c r="E61" s="33">
         <v>2.17</v>
       </c>
-      <c r="F61" s="32">
+      <c r="F61" s="33">
         <v>2.64</v>
       </c>
-      <c r="G61" s="32">
+      <c r="G61" s="33">
         <v>2.39</v>
       </c>
-      <c r="H61" s="32">
+      <c r="H61" s="33">
         <v>2.09</v>
       </c>
-      <c r="I61" s="32">
+      <c r="I61" s="33">
         <v>2.24</v>
       </c>
-      <c r="J61" s="32">
+      <c r="J61" s="33">
         <v>2.34</v>
       </c>
-      <c r="K61" s="32">
+      <c r="K61" s="33">
         <v>2.48</v>
       </c>
-      <c r="L61" s="32">
+      <c r="L61" s="33">
         <v>2.11</v>
       </c>
-      <c r="M61" s="32">
+      <c r="M61" s="33">
         <v>2.38</v>
       </c>
-      <c r="N61" s="32">
+      <c r="N61" s="33">
         <v>2.11</v>
       </c>
-      <c r="O61" s="32">
+      <c r="O61" s="33">
         <v>2.2</v>
       </c>
-      <c r="P61" s="32">
+      <c r="P61" s="33">
         <v>4.08</v>
       </c>
-      <c r="Q61" s="32">
+      <c r="Q61" s="33">
         <v>4.06</v>
       </c>
-      <c r="R61" s="32">
+      <c r="R61" s="33">
         <v>5.3</v>
       </c>
-      <c r="S61" s="32">
+      <c r="S61" s="33">
         <v>8.18</v>
       </c>
-      <c r="T61" s="31"/>
+      <c r="T61" s="32"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="29" t="s">
-        <v>378</v>
-      </c>
-      <c r="B62" s="32">
+      <c r="A62" s="30" t="s">
+        <v>379</v>
+      </c>
+      <c r="B62" s="33">
         <v>2.44</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="33">
         <v>2.41</v>
       </c>
-      <c r="D62" s="32">
+      <c r="D62" s="33">
         <v>2.36</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="33">
         <v>2.31</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="33">
         <v>2.36</v>
       </c>
-      <c r="G62" s="32">
+      <c r="G62" s="33">
         <v>2.29</v>
       </c>
-      <c r="H62" s="32">
+      <c r="H62" s="33">
         <v>2.23</v>
       </c>
-      <c r="I62" s="32">
+      <c r="I62" s="33">
         <v>2.3</v>
       </c>
-      <c r="J62" s="32">
+      <c r="J62" s="33">
         <v>2.29</v>
       </c>
-      <c r="K62" s="32">
+      <c r="K62" s="33">
         <v>2.26</v>
       </c>
-      <c r="L62" s="32">
+      <c r="L62" s="33">
         <v>2.46</v>
       </c>
-      <c r="M62" s="32">
+      <c r="M62" s="33">
         <v>2.79</v>
       </c>
-      <c r="N62" s="32">
+      <c r="N62" s="33">
         <v>3.24</v>
       </c>
-      <c r="O62" s="32">
+      <c r="O62" s="33">
         <v>4.24</v>
       </c>
-      <c r="P62" s="31"/>
-      <c r="Q62" s="31"/>
-      <c r="R62" s="31"/>
-      <c r="S62" s="31"/>
-      <c r="T62" s="31"/>
+      <c r="P62" s="32"/>
+      <c r="Q62" s="32"/>
+      <c r="R62" s="32"/>
+      <c r="S62" s="32"/>
+      <c r="T62" s="32"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="27" t="s">
-        <v>379</v>
-      </c>
-      <c r="B63" s="28"/>
-      <c r="C63" s="28"/>
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="28"/>
-      <c r="I63" s="28"/>
-      <c r="J63" s="28"/>
-      <c r="K63" s="28"/>
-      <c r="L63" s="28"/>
-      <c r="M63" s="28"/>
-      <c r="N63" s="28"/>
-      <c r="O63" s="28"/>
-      <c r="P63" s="28"/>
-      <c r="Q63" s="28"/>
-      <c r="R63" s="28"/>
-      <c r="S63" s="28"/>
-      <c r="T63" s="28"/>
+      <c r="A63" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="29"/>
+      <c r="E63" s="29"/>
+      <c r="F63" s="29"/>
+      <c r="G63" s="29"/>
+      <c r="H63" s="29"/>
+      <c r="I63" s="29"/>
+      <c r="J63" s="29"/>
+      <c r="K63" s="29"/>
+      <c r="L63" s="29"/>
+      <c r="M63" s="29"/>
+      <c r="N63" s="29"/>
+      <c r="O63" s="29"/>
+      <c r="P63" s="29"/>
+      <c r="Q63" s="29"/>
+      <c r="R63" s="29"/>
+      <c r="S63" s="29"/>
+      <c r="T63" s="29"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="29" t="s">
-        <v>380</v>
-      </c>
-      <c r="B64" s="32">
+      <c r="A64" s="30" t="s">
+        <v>381</v>
+      </c>
+      <c r="B64" s="33">
         <v>10.97</v>
       </c>
-      <c r="C64" s="32">
+      <c r="C64" s="33">
         <v>15.26</v>
       </c>
-      <c r="D64" s="32">
+      <c r="D64" s="33">
         <v>12.27</v>
       </c>
-      <c r="E64" s="32">
+      <c r="E64" s="33">
         <v>11.28</v>
       </c>
-      <c r="F64" s="32">
+      <c r="F64" s="33">
         <v>13.34</v>
       </c>
-      <c r="G64" s="32">
+      <c r="G64" s="33">
         <v>10.69</v>
       </c>
-      <c r="H64" s="32">
+      <c r="H64" s="33">
         <v>14.94</v>
       </c>
-      <c r="I64" s="32">
+      <c r="I64" s="33">
         <v>27.18</v>
       </c>
-      <c r="J64" s="32">
+      <c r="J64" s="33">
         <v>35.15</v>
       </c>
-      <c r="K64" s="32">
+      <c r="K64" s="33">
         <v>14.38</v>
       </c>
-      <c r="L64" s="32">
+      <c r="L64" s="33">
         <v>16.12</v>
       </c>
-      <c r="M64" s="32">
+      <c r="M64" s="33">
         <v>32.21</v>
       </c>
-      <c r="N64" s="31"/>
-      <c r="O64" s="32">
+      <c r="N64" s="32"/>
+      <c r="O64" s="33">
         <v>42.3</v>
       </c>
-      <c r="P64" s="31"/>
-      <c r="Q64" s="31"/>
-      <c r="R64" s="31"/>
-      <c r="S64" s="31"/>
-      <c r="T64" s="31"/>
+      <c r="P64" s="32"/>
+      <c r="Q64" s="32"/>
+      <c r="R64" s="32"/>
+      <c r="S64" s="32"/>
+      <c r="T64" s="32"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="29" t="s">
-        <v>381</v>
-      </c>
-      <c r="B65" s="32">
+      <c r="A65" s="30" t="s">
+        <v>382</v>
+      </c>
+      <c r="B65" s="33">
         <v>12.45</v>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="33">
         <v>12.52</v>
       </c>
-      <c r="D65" s="32">
+      <c r="D65" s="33">
         <v>12.2</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="33">
         <v>13.14</v>
       </c>
-      <c r="F65" s="32">
+      <c r="F65" s="33">
         <v>14.89</v>
       </c>
-      <c r="G65" s="32">
+      <c r="G65" s="33">
         <v>15.44</v>
       </c>
-      <c r="H65" s="32">
+      <c r="H65" s="33">
         <v>19.01</v>
       </c>
-      <c r="I65" s="32">
+      <c r="I65" s="33">
         <v>22.54</v>
       </c>
-      <c r="J65" s="32">
+      <c r="J65" s="33">
         <v>25.81</v>
       </c>
-      <c r="K65" s="32">
+      <c r="K65" s="33">
         <v>25.87</v>
       </c>
-      <c r="L65" s="31"/>
-      <c r="M65" s="31"/>
-      <c r="N65" s="31"/>
-      <c r="O65" s="31"/>
-      <c r="P65" s="31"/>
-      <c r="Q65" s="31"/>
-      <c r="R65" s="31"/>
-      <c r="S65" s="31"/>
-      <c r="T65" s="31"/>
+      <c r="L65" s="32"/>
+      <c r="M65" s="32"/>
+      <c r="N65" s="32"/>
+      <c r="O65" s="32"/>
+      <c r="P65" s="32"/>
+      <c r="Q65" s="32"/>
+      <c r="R65" s="32"/>
+      <c r="S65" s="32"/>
+      <c r="T65" s="32"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="27" t="s">
-        <v>382</v>
-      </c>
-      <c r="B66" s="28"/>
-      <c r="C66" s="28"/>
-      <c r="D66" s="28"/>
-      <c r="E66" s="28"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
-      <c r="H66" s="28"/>
-      <c r="I66" s="28"/>
-      <c r="J66" s="28"/>
-      <c r="K66" s="28"/>
-      <c r="L66" s="28"/>
-      <c r="M66" s="28"/>
-      <c r="N66" s="28"/>
-      <c r="O66" s="28"/>
-      <c r="P66" s="28"/>
-      <c r="Q66" s="28"/>
-      <c r="R66" s="28"/>
-      <c r="S66" s="28"/>
-      <c r="T66" s="28"/>
+      <c r="A66" s="28" t="s">
+        <v>383</v>
+      </c>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="29"/>
+      <c r="E66" s="29"/>
+      <c r="F66" s="29"/>
+      <c r="G66" s="29"/>
+      <c r="H66" s="29"/>
+      <c r="I66" s="29"/>
+      <c r="J66" s="29"/>
+      <c r="K66" s="29"/>
+      <c r="L66" s="29"/>
+      <c r="M66" s="29"/>
+      <c r="N66" s="29"/>
+      <c r="O66" s="29"/>
+      <c r="P66" s="29"/>
+      <c r="Q66" s="29"/>
+      <c r="R66" s="29"/>
+      <c r="S66" s="29"/>
+      <c r="T66" s="29"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="29" t="s">
-        <v>383</v>
-      </c>
-      <c r="B67" s="32">
+      <c r="A67" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="B67" s="33">
         <v>28.53</v>
       </c>
-      <c r="C67" s="32">
+      <c r="C67" s="33">
         <v>12.12</v>
       </c>
-      <c r="D67" s="32">
+      <c r="D67" s="33">
         <v>17.31</v>
       </c>
-      <c r="E67" s="32">
+      <c r="E67" s="33">
         <v>19.79</v>
       </c>
-      <c r="F67" s="32">
+      <c r="F67" s="33">
         <v>20.43</v>
       </c>
-      <c r="G67" s="32">
+      <c r="G67" s="33">
         <v>11.69</v>
       </c>
-      <c r="H67" s="32">
+      <c r="H67" s="33">
         <v>67.29</v>
       </c>
-      <c r="I67" s="32">
+      <c r="I67" s="33">
         <v>41.58</v>
       </c>
-      <c r="J67" s="30">
+      <c r="J67" s="31">
         <v>198.04</v>
       </c>
-      <c r="K67" s="31"/>
-      <c r="L67" s="31"/>
-      <c r="M67" s="32">
+      <c r="K67" s="32"/>
+      <c r="L67" s="32"/>
+      <c r="M67" s="33">
         <v>34.65</v>
       </c>
-      <c r="N67" s="31"/>
-      <c r="O67" s="32">
+      <c r="N67" s="32"/>
+      <c r="O67" s="33">
         <v>28.06</v>
       </c>
-      <c r="P67" s="32">
+      <c r="P67" s="33">
         <v>21.9</v>
       </c>
-      <c r="Q67" s="31"/>
-      <c r="R67" s="31"/>
-      <c r="S67" s="31"/>
-      <c r="T67" s="31"/>
+      <c r="Q67" s="32"/>
+      <c r="R67" s="32"/>
+      <c r="S67" s="32"/>
+      <c r="T67" s="32"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="29" t="s">
-        <v>384</v>
-      </c>
-      <c r="B68" s="32">
+      <c r="A68" s="30" t="s">
+        <v>385</v>
+      </c>
+      <c r="B68" s="33">
         <v>18.11</v>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="33">
         <v>15.24</v>
       </c>
-      <c r="D68" s="32">
+      <c r="D68" s="33">
         <v>18.45</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68" s="33">
         <v>20.37</v>
       </c>
-      <c r="F68" s="32">
+      <c r="F68" s="33">
         <v>22.97</v>
       </c>
-      <c r="G68" s="32">
+      <c r="G68" s="33">
         <v>30.22</v>
       </c>
-      <c r="H68" s="30">
+      <c r="H68" s="31">
         <v>197.65</v>
       </c>
-      <c r="I68" s="30">
+      <c r="I68" s="31">
         <v>170.13</v>
       </c>
-      <c r="J68" s="31"/>
-      <c r="K68" s="30">
+      <c r="J68" s="32"/>
+      <c r="K68" s="31">
         <v>697.18</v>
       </c>
-      <c r="L68" s="32">
+      <c r="L68" s="33">
         <v>56.31</v>
       </c>
-      <c r="M68" s="30">
+      <c r="M68" s="31">
         <v>335.45</v>
       </c>
-      <c r="N68" s="31"/>
-      <c r="O68" s="31"/>
-      <c r="P68" s="31"/>
-      <c r="Q68" s="31"/>
-      <c r="R68" s="31"/>
-      <c r="S68" s="31"/>
-      <c r="T68" s="31"/>
+      <c r="N68" s="32"/>
+      <c r="O68" s="32"/>
+      <c r="P68" s="32"/>
+      <c r="Q68" s="32"/>
+      <c r="R68" s="32"/>
+      <c r="S68" s="32"/>
+      <c r="T68" s="32"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="27" t="s">
-        <v>385</v>
-      </c>
-      <c r="B69" s="28"/>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="28"/>
-      <c r="J69" s="28"/>
-      <c r="K69" s="28"/>
-      <c r="L69" s="28"/>
-      <c r="M69" s="28"/>
-      <c r="N69" s="28"/>
-      <c r="O69" s="28"/>
-      <c r="P69" s="28"/>
-      <c r="Q69" s="28"/>
-      <c r="R69" s="28"/>
-      <c r="S69" s="28"/>
-      <c r="T69" s="28"/>
+      <c r="A69" s="28" t="s">
+        <v>386</v>
+      </c>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
+      <c r="E69" s="29"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
+      <c r="I69" s="29"/>
+      <c r="J69" s="29"/>
+      <c r="K69" s="29"/>
+      <c r="L69" s="29"/>
+      <c r="M69" s="29"/>
+      <c r="N69" s="29"/>
+      <c r="O69" s="29"/>
+      <c r="P69" s="29"/>
+      <c r="Q69" s="29"/>
+      <c r="R69" s="29"/>
+      <c r="S69" s="29"/>
+      <c r="T69" s="29"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="29" t="s">
-        <v>386</v>
-      </c>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="32">
+      <c r="A70" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="33">
         <v>64.73</v>
       </c>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
-      <c r="J70" s="31"/>
-      <c r="K70" s="31"/>
-      <c r="L70" s="31"/>
-      <c r="M70" s="31"/>
-      <c r="N70" s="31"/>
-      <c r="O70" s="31"/>
-      <c r="P70" s="31"/>
-      <c r="Q70" s="31"/>
-      <c r="R70" s="31"/>
-      <c r="S70" s="31"/>
-      <c r="T70" s="31"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
+      <c r="J70" s="32"/>
+      <c r="K70" s="32"/>
+      <c r="L70" s="32"/>
+      <c r="M70" s="32"/>
+      <c r="N70" s="32"/>
+      <c r="O70" s="32"/>
+      <c r="P70" s="32"/>
+      <c r="Q70" s="32"/>
+      <c r="R70" s="32"/>
+      <c r="S70" s="32"/>
+      <c r="T70" s="32"/>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
     <row r="72" ht="15.75" customHeight="1"/>
